--- a/12309365.xlsx
+++ b/12309365.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFA93408-DFA4-4AC8-9E71-09D8AEA4B644}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96553B0D-08C4-4022-BF91-88BE71E74485}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t xml:space="preserve">Preaparing for networking ca </t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>Prepare for my ca in DBMS</t>
+  </si>
+  <si>
+    <t>revise  prevoius topic in c++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">not satisfied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suffering From Fever </t>
   </si>
 </sst>
 </file>
@@ -537,10 +555,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1363,7 +1377,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B13" s="14">
         <v>500</v>
@@ -1408,70 +1422,142 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46242</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>50</v>
+      </c>
+      <c r="F14" s="14">
+        <v>480</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>480</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B16" s="14">
+        <v>600</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>40</v>
+      </c>
+      <c r="E16" s="14">
+        <v>20</v>
+      </c>
+      <c r="F16" s="14">
+        <v>360</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>20</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12309365.xlsx
+++ b/12309365.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96553B0D-08C4-4022-BF91-88BE71E74485}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD8C2FC3-CA22-4A91-B64E-F636F058DEDF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,21 @@
   </si>
   <si>
     <t xml:space="preserve">Suffering From Fever </t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">satisfied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning python </t>
+  </si>
+  <si>
+    <t xml:space="preserve">good </t>
+  </si>
+  <si>
+    <t>preaparing for English Presentation.</t>
   </si>
 </sst>
 </file>
@@ -555,6 +570,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1560,48 +1579,96 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B17" s="14">
+        <v>500</v>
+      </c>
+      <c r="C17" s="14">
+        <v>50</v>
+      </c>
+      <c r="D17" s="14">
+        <v>30</v>
+      </c>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>360</v>
+      </c>
+      <c r="G17" s="14">
+        <v>7</v>
+      </c>
+      <c r="H17" s="14">
+        <v>100</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>70</v>
+      </c>
+      <c r="E18" s="14">
+        <v>80</v>
+      </c>
+      <c r="F18" s="14">
+        <v>480</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>120</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12309365.xlsx
+++ b/12309365.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD8C2FC3-CA22-4A91-B64E-F636F058DEDF}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A90D0EA6-1C20-47BC-9B9E-8FD6DE5DA23B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,15 @@
   </si>
   <si>
     <t>preaparing for English Presentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busy in somework </t>
+  </si>
+  <si>
+    <t>staisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning python from youtube </t>
   </si>
 </sst>
 </file>
@@ -1671,48 +1680,96 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B19" s="14">
+        <v>500</v>
+      </c>
+      <c r="C19" s="14">
+        <v>70</v>
+      </c>
+      <c r="D19" s="14">
+        <v>50</v>
+      </c>
+      <c r="E19" s="14">
+        <v>50</v>
+      </c>
+      <c r="F19" s="14">
+        <v>400</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>70</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>80</v>
+      </c>
+      <c r="D20" s="14">
+        <v>80</v>
+      </c>
+      <c r="E20" s="14">
+        <v>20</v>
+      </c>
+      <c r="F20" s="14">
+        <v>480</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>80</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
